--- a/diseases/d065/2000-2004.xlsx
+++ b/diseases/d065/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2229,6 +2279,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2374,6 +2429,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2519,6 +2579,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2664,6 +2729,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2809,6 +2879,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2954,6 +3029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3099,6 +3179,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3244,6 +3329,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3392,6 +3482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3682,6 +3782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3827,6 +3932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3972,6 +4082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4117,6 +4232,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4262,6 +4382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4407,6 +4532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4552,6 +4682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4700,6 +4835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4845,6 +4985,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4990,6 +5135,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5135,6 +5285,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5280,6 +5435,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5425,6 +5585,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5570,6 +5735,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5715,6 +5885,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5860,6 +6035,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6008,6 +6188,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6153,6 +6338,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6298,6 +6488,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6443,6 +6638,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6588,6 +6788,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6733,6 +6938,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6878,6 +7088,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7023,6 +7238,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7168,6 +7388,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7316,6 +7541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7691,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7606,6 +7841,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7751,6 +7991,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7896,6 +8141,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8041,6 +8291,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8186,6 +8441,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8331,6 +8591,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8476,6 +8741,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8624,6 +8894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8769,6 +9044,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8914,6 +9194,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9059,6 +9344,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9204,6 +9494,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9349,6 +9644,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9494,6 +9794,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9639,6 +9944,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9784,6 +10094,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9932,6 +10247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10077,6 +10397,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10222,6 +10547,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10367,6 +10697,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10512,6 +10847,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10657,6 +10997,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10802,6 +11147,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10947,6 +11297,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11092,6 +11447,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11240,6 +11600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11385,6 +11750,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11530,6 +11900,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11675,6 +12050,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11820,6 +12200,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11965,6 +12350,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12110,6 +12500,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12255,6 +12650,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12400,6 +12800,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12548,6 +12953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12693,6 +13103,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12838,6 +13253,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12983,6 +13403,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13128,6 +13553,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13273,6 +13703,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13418,6 +13853,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13563,6 +14003,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13708,6 +14153,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13856,6 +14306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14001,6 +14456,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14146,6 +14606,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14291,6 +14756,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14436,6 +14906,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14581,6 +15056,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14726,6 +15206,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14871,6 +15356,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15016,6 +15506,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15164,6 +15659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15309,6 +15809,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15454,6 +15959,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15599,6 +16109,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15744,6 +16259,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15889,6 +16409,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16034,6 +16559,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16179,6 +16709,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16324,6 +16859,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16472,6 +17012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16617,6 +17162,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16762,6 +17312,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16907,6 +17462,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17052,6 +17612,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17197,6 +17762,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17342,6 +17912,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17487,6 +18062,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17632,6 +18212,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17780,6 +18365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17925,6 +18515,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18070,6 +18665,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18215,6 +18815,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18360,6 +18965,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18505,6 +19115,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18650,6 +19265,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18795,6 +19415,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18940,6 +19565,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19088,6 +19718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19233,6 +19868,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19378,6 +20018,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19523,6 +20168,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19668,6 +20318,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19813,6 +20468,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19958,6 +20618,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20103,6 +20768,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20248,6 +20918,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20396,6 +21071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20541,6 +21221,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20686,6 +21371,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20831,6 +21521,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20976,6 +21671,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21121,6 +21821,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21266,6 +21971,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21411,6 +22121,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21556,6 +22271,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21704,6 +22424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21849,6 +22574,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21994,6 +22724,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22139,6 +22874,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22284,6 +23024,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22429,6 +23174,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22574,6 +23324,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22719,6 +23474,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22864,6 +23624,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23012,6 +23777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23157,6 +23927,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23302,6 +24077,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23447,6 +24227,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23592,6 +24377,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23737,6 +24527,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23882,6 +24677,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24027,6 +24827,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24172,6 +24977,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24320,6 +25130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24465,6 +25280,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24610,6 +25430,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24755,6 +25580,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25730,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25045,6 +25880,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25190,6 +26030,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25335,6 +26180,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25480,6 +26330,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25628,6 +26483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25773,6 +26633,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25918,6 +26783,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26063,6 +26933,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26208,6 +27083,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26353,6 +27233,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26498,6 +27383,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26643,6 +27533,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26788,6 +27683,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26936,6 +27836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27081,6 +27986,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27226,6 +28136,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27371,6 +28286,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27516,6 +28436,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27661,6 +28586,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27806,6 +28736,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27951,6 +28886,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28096,6 +29036,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28244,6 +29189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28389,6 +29339,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28534,6 +29489,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28679,6 +29639,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28824,6 +29789,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28969,6 +29939,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29114,6 +30089,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29259,6 +30239,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29404,6 +30389,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29552,6 +30542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29697,6 +30692,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29842,6 +30842,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29987,6 +30992,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30132,6 +31142,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30277,6 +31292,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30422,6 +31442,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30567,6 +31592,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30712,6 +31742,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30860,6 +31895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31005,6 +32045,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31150,6 +32195,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31295,6 +32345,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31440,6 +32495,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31585,6 +32645,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31730,6 +32795,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31875,6 +32945,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32020,6 +33095,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32168,6 +33248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32313,6 +33398,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32458,6 +33548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32603,6 +33698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32748,6 +33848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32893,6 +33998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33038,6 +34148,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33183,6 +34298,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33328,6 +34448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33476,6 +34601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33621,6 +34751,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33766,6 +34901,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33911,6 +35051,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34056,6 +35201,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34201,6 +35351,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34346,6 +35501,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34491,6 +35651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34636,6 +35801,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34784,6 +35954,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34929,6 +36104,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35074,6 +36254,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35219,6 +36404,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35364,6 +36554,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35509,6 +36704,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35654,6 +36854,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35799,6 +37004,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35944,6 +37154,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36092,6 +37307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36237,6 +37457,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36382,6 +37607,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36527,6 +37757,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36672,6 +37907,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36817,6 +38057,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36962,6 +38207,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37107,6 +38357,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37252,6 +38507,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37400,6 +38660,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37545,6 +38810,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37690,6 +38960,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37835,6 +39110,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37980,6 +39260,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38125,6 +39410,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38270,6 +39560,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38415,6 +39710,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38560,6 +39860,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38708,6 +40013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38853,6 +40163,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38998,6 +40313,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39143,6 +40463,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39288,6 +40613,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39433,6 +40763,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39578,6 +40913,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39723,6 +41063,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39868,6 +41213,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40016,6 +41366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40161,6 +41516,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40306,6 +41666,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40451,6 +41816,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40596,6 +41966,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40741,6 +42116,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40886,6 +42266,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41031,6 +42416,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41176,6 +42566,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41324,6 +42719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41469,6 +42869,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41614,6 +43019,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41759,6 +43169,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41904,6 +43319,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42049,6 +43469,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42194,6 +43619,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42339,6 +43769,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42484,6 +43919,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42632,6 +44072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42777,6 +44222,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42922,6 +44372,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43067,6 +44522,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43212,6 +44672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43357,6 +44822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43502,6 +44972,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43647,6 +45122,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43792,6 +45272,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43940,6 +45425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44085,6 +45575,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44230,6 +45725,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44375,6 +45875,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44520,6 +46025,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44665,6 +46175,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44810,6 +46325,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44955,6 +46475,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45100,6 +46625,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45248,6 +46778,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45393,6 +46928,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45538,6 +47078,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45683,6 +47228,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45828,6 +47378,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45973,6 +47528,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46118,6 +47678,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46263,6 +47828,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46408,6 +47978,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46556,6 +48131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46701,6 +48281,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46846,6 +48431,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46991,6 +48581,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47136,6 +48731,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47281,6 +48881,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47426,6 +49031,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47571,6 +49181,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47716,6 +49331,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47864,6 +49484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48009,6 +49634,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48154,6 +49784,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48299,6 +49934,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48444,6 +50084,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48589,6 +50234,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48734,6 +50384,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48879,6 +50534,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49024,6 +50684,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49172,6 +50837,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49317,6 +50987,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49462,6 +51137,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49607,6 +51287,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49752,6 +51437,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49897,6 +51587,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50042,6 +51737,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50187,6 +51887,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50332,6 +52037,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50480,6 +52190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50625,6 +52340,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50770,6 +52490,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50915,6 +52640,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51060,6 +52790,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51205,6 +52940,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51350,6 +53090,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51495,6 +53240,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51640,6 +53390,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51788,6 +53543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51933,6 +53693,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52078,6 +53843,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52223,6 +53993,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52368,6 +54143,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52513,6 +54293,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52658,6 +54443,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52803,6 +54593,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52948,6 +54743,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53096,6 +54896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53241,6 +55046,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53386,6 +55196,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53531,6 +55346,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53676,6 +55496,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53821,6 +55646,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53966,6 +55796,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54111,6 +55946,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54256,6 +56096,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54404,6 +56249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54549,6 +56399,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54694,6 +56549,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54839,6 +56699,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54984,6 +56849,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55129,6 +56999,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55274,6 +57149,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55419,6 +57299,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55564,6 +57449,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55712,6 +57602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55857,6 +57752,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56002,6 +57902,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56147,6 +58052,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56292,6 +58202,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56437,6 +58352,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56582,6 +58502,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56727,6 +58652,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56872,6 +58802,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57020,6 +58955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57165,6 +59105,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57310,6 +59255,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57455,6 +59405,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57600,6 +59555,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57745,6 +59705,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57890,6 +59855,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58035,6 +60005,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58180,6 +60155,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58328,6 +60308,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58473,6 +60458,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58618,6 +60608,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58763,6 +60758,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58908,6 +60908,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59053,6 +61058,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59198,6 +61208,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59343,6 +61358,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59488,6 +61508,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59636,6 +61661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59781,6 +61811,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59926,6 +61961,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60071,6 +62111,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60216,6 +62261,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60361,6 +62411,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60506,6 +62561,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60651,6 +62711,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60796,6 +62861,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60944,6 +63014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61089,6 +63164,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61234,6 +63314,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61379,6 +63464,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61524,6 +63614,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61669,6 +63764,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61814,6 +63914,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61959,6 +64064,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62104,6 +64214,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62252,6 +64367,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62397,6 +64517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62542,6 +64667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62687,6 +64817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62832,6 +64967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62977,6 +65117,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63122,6 +65267,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63267,6 +65417,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63412,6 +65567,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63560,6 +65720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63705,6 +65870,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63850,6 +66020,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63995,6 +66170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64140,6 +66320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64285,6 +66470,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64430,6 +66620,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64575,6 +66770,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64720,6 +66920,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64868,6 +67073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65013,6 +67223,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65158,6 +67373,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65303,6 +67523,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65448,6 +67673,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65593,6 +67823,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65738,6 +67973,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65883,6 +68123,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66028,6 +68273,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66176,6 +68426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66321,6 +68576,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66466,6 +68726,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO454" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66611,6 +68876,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO455" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66756,6 +69026,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66901,6 +69176,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO457" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67046,6 +69326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67191,6 +69476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67336,6 +69626,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO460" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67484,6 +69779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO461" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67629,6 +69929,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO462" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67774,6 +70079,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO463" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67919,6 +70229,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO464" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68064,6 +70379,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68209,6 +70529,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO466" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68354,6 +70679,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO467" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68499,6 +70829,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO468" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68644,6 +70979,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68792,6 +71132,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO470" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68937,6 +71282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO471" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69082,6 +71432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69227,6 +71582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO473" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69372,6 +71732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69517,6 +71882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO475" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69662,6 +72032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO476" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69807,6 +72182,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO477" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69952,6 +72332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO478" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70100,6 +72485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA479" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO479" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70245,6 +72635,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO480" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70390,6 +72785,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO481" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70535,6 +72935,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO482" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70680,6 +73085,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO483" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70825,6 +73235,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO484" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70970,6 +73385,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO485" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71115,6 +73535,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO486" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71260,6 +73685,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO487" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71408,6 +73838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA488" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO488" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71553,6 +73988,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO489" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71698,6 +74138,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO490" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71843,6 +74288,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO491" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71988,6 +74438,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA492" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO492" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72133,6 +74588,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO493" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72278,6 +74738,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO494" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72423,6 +74888,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO495" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72568,6 +75038,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA496" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO496" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72716,6 +75191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO497" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72861,6 +75341,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO498" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73006,6 +75491,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA499" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO499" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73151,6 +75641,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA500" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO500" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73296,6 +75791,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO501" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73441,6 +75941,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO502" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73586,6 +76091,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO503" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73731,6 +76241,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO504" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73876,6 +76391,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO505" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74024,6 +76544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO506" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74169,6 +76694,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO507" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74314,6 +76844,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO508" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74459,6 +76994,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA509" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO509" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74604,6 +77144,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO510" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74749,6 +77294,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO511" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74894,6 +77444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA512" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO512" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75039,6 +77594,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA513" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO513" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75184,6 +77744,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA514" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO514" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75332,6 +77897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA515" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO515" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75477,6 +78047,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO516" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75622,6 +78197,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO517" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75767,6 +78347,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO518" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75912,6 +78497,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO519" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76057,6 +78647,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO520" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76202,6 +78797,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO521" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76347,6 +78947,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO522" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76492,6 +79097,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO523" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76640,6 +79250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO524" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76785,6 +79400,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO525" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76930,6 +79550,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA526" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO526" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77075,6 +79700,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO527" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77220,6 +79850,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO528" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77365,6 +80000,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO529" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77510,6 +80150,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA530" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO530" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77655,6 +80300,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO531" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77800,6 +80450,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO532" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77948,6 +80603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO533" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78093,6 +80753,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO534" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78238,6 +80903,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO535" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78383,6 +81053,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO536" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78528,6 +81203,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO537" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78673,6 +81353,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO538" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78818,6 +81503,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO539" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78963,6 +81653,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO540" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -79106,6 +81801,11 @@
       <c r="S541" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO541" t="inlineStr">
